--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Reed-Beverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BB2B139-0406-43CF-8BD7-3820DFFFC1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078F456-1FDA-4550-B018-FF25147E0E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Reed-Beverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74316AEF-8022-4950-A005-50D5C690EF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D011F8F-CAC4-43E9-941E-2B2A578649DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="56">
   <si>
     <t>Company Name</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Speed Mangement-C</t>
+  </si>
+  <si>
+    <t>Vehicle Inspection</t>
   </si>
   <si>
     <t>Reed Beverage</t>
@@ -577,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -626,13 +629,13 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>5344</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>18</v>
@@ -655,13 +658,13 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>5319</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -684,13 +687,13 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>5320</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -713,13 +716,13 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>5321</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>18</v>
@@ -751,13 +754,13 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>5347</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>18</v>
@@ -789,13 +792,13 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>5345</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
@@ -818,13 +821,13 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>5323</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>18</v>
@@ -856,13 +859,13 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12">
         <v>5324</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>18</v>
@@ -885,13 +888,13 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>5336</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>18</v>
@@ -914,13 +917,13 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14">
         <v>5346</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>18</v>
@@ -943,13 +946,13 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <v>5326</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>18</v>
@@ -972,13 +975,13 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16">
         <v>5327</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>18</v>
@@ -1010,13 +1013,13 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18">
         <v>5328</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>18</v>
@@ -1039,13 +1042,13 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19">
         <v>5330</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>18</v>
@@ -1068,13 +1071,13 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20">
         <v>5343</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>18</v>
@@ -1106,13 +1109,13 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22">
         <v>5325</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>18</v>
@@ -1135,13 +1138,13 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23">
         <v>5322</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>18</v>
@@ -1164,13 +1167,13 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <v>5340</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>18</v>
@@ -1193,13 +1196,13 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25">
         <v>5329</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>18</v>
@@ -1231,13 +1234,13 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27">
         <v>5318</v>
       </c>
       <c r="F27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>18</v>
@@ -1269,13 +1272,13 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29">
         <v>5333</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>18</v>
@@ -1298,13 +1301,13 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30">
         <v>5331</v>
       </c>
       <c r="F30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>18</v>
@@ -1327,13 +1330,13 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31">
         <v>5332</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>18</v>
@@ -1356,13 +1359,13 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32">
         <v>5334</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>18</v>
@@ -1385,13 +1388,13 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33">
         <v>5335</v>
       </c>
       <c r="F33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>18</v>
@@ -1423,13 +1426,13 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35">
         <v>5339</v>
       </c>
       <c r="F35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>18</v>
@@ -1452,13 +1455,13 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36">
         <v>5337</v>
       </c>
       <c r="F36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>18</v>
@@ -1481,13 +1484,13 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E37">
         <v>5338</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>18</v>
@@ -1510,13 +1513,13 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E38">
         <v>5341</v>
       </c>
       <c r="F38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>18</v>
@@ -1539,13 +1542,13 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E39">
         <v>5342</v>
       </c>
       <c r="F39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>18</v>
@@ -1568,13 +1571,13 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E40">
         <v>5344</v>
       </c>
       <c r="F40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>17</v>
@@ -1597,13 +1600,13 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E41">
         <v>5324</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>17</v>
@@ -1626,13 +1629,13 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E42">
         <v>5341</v>
       </c>
       <c r="F42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>17</v>
@@ -1655,13 +1658,13 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E43">
         <v>5332</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>17</v>
@@ -1684,13 +1687,13 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E44">
         <v>5345</v>
       </c>
       <c r="F44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>17</v>
@@ -1713,13 +1716,13 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E45">
         <v>5336</v>
       </c>
       <c r="F45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>17</v>
@@ -1751,13 +1754,13 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E47">
         <v>5346</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>17</v>
@@ -1780,13 +1783,13 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E48">
         <v>5320</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>17</v>
@@ -1809,13 +1812,13 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E49">
         <v>5343</v>
       </c>
       <c r="F49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>17</v>
@@ -1838,13 +1841,13 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50">
         <v>5325</v>
       </c>
       <c r="F50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>17</v>
@@ -1867,13 +1870,13 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E51">
         <v>5342</v>
       </c>
       <c r="F51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>17</v>
@@ -1896,13 +1899,13 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E52">
         <v>5322</v>
       </c>
       <c r="F52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>17</v>
@@ -1925,13 +1928,13 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53">
         <v>5330</v>
       </c>
       <c r="F53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>17</v>
@@ -1954,13 +1957,13 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E54">
         <v>5340</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>17</v>
@@ -1983,13 +1986,13 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E55">
         <v>5329</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>17</v>
@@ -2012,13 +2015,13 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E56">
         <v>5318</v>
       </c>
       <c r="F56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>17</v>
@@ -2041,13 +2044,13 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E57">
         <v>5333</v>
       </c>
       <c r="F57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>17</v>
@@ -2070,13 +2073,13 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E58">
         <v>5339</v>
       </c>
       <c r="F58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>17</v>
@@ -2108,13 +2111,13 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E60">
         <v>5338</v>
       </c>
       <c r="F60" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>17</v>
@@ -2137,13 +2140,13 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E61">
         <v>5335</v>
       </c>
       <c r="F61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>17</v>
@@ -2166,13 +2169,13 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E62">
         <v>5321</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>17</v>
@@ -2195,13 +2198,13 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E63">
         <v>5337</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>17</v>
@@ -2224,13 +2227,13 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E64">
         <v>5334</v>
       </c>
       <c r="F64" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>17</v>
@@ -2253,13 +2256,13 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E65">
         <v>5328</v>
       </c>
       <c r="F65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>17</v>
@@ -2282,13 +2285,13 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E66">
         <v>5326</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>17</v>
@@ -2311,13 +2314,13 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E67">
         <v>5319</v>
       </c>
       <c r="F67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>17</v>
@@ -2340,13 +2343,13 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E68">
         <v>5323</v>
       </c>
       <c r="F68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>17</v>
@@ -2369,13 +2372,13 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E69">
         <v>5347</v>
       </c>
       <c r="F69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>17</v>
@@ -2398,13 +2401,13 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E70">
         <v>5341</v>
       </c>
       <c r="F70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -2427,13 +2430,13 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E71">
         <v>5320</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -2456,13 +2459,13 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E72">
         <v>5330</v>
       </c>
       <c r="F72" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -2485,13 +2488,13 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E73">
         <v>5335</v>
       </c>
       <c r="F73" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -2514,13 +2517,13 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E74">
         <v>5344</v>
       </c>
       <c r="F74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>19</v>
@@ -2543,13 +2546,13 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E75">
         <v>5345</v>
       </c>
       <c r="F75" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>19</v>
@@ -2572,13 +2575,13 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E76">
         <v>5336</v>
       </c>
       <c r="F76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>19</v>
@@ -2610,13 +2613,13 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E78">
         <v>5766</v>
       </c>
       <c r="F78" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>19</v>
@@ -2639,13 +2642,13 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E79">
         <v>5346</v>
       </c>
       <c r="F79" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>19</v>
@@ -2668,13 +2671,13 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E80">
         <v>5767</v>
       </c>
       <c r="F80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>19</v>
@@ -2697,13 +2700,13 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E81">
         <v>5343</v>
       </c>
       <c r="F81" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>19</v>
@@ -2726,13 +2729,13 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E82">
         <v>5322</v>
       </c>
       <c r="F82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>19</v>
@@ -2755,13 +2758,13 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E83">
         <v>5768</v>
       </c>
       <c r="F83" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>19</v>
@@ -2784,13 +2787,13 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E84">
         <v>5340</v>
       </c>
       <c r="F84" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>19</v>
@@ -2813,13 +2816,13 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E85">
         <v>5329</v>
       </c>
       <c r="F85" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>19</v>
@@ -2842,13 +2845,13 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E86">
         <v>5318</v>
       </c>
       <c r="F86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>19</v>
@@ -2871,13 +2874,13 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E87">
         <v>5333</v>
       </c>
       <c r="F87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>19</v>
@@ -2900,13 +2903,13 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E88">
         <v>5338</v>
       </c>
       <c r="F88" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>19</v>
@@ -2929,13 +2932,13 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E89">
         <v>5321</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>19</v>
@@ -2958,13 +2961,13 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E90">
         <v>5337</v>
       </c>
       <c r="F90" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>19</v>
@@ -2987,13 +2990,13 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E91">
         <v>5334</v>
       </c>
       <c r="F91" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>19</v>
@@ -3016,13 +3019,13 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E92">
         <v>5582</v>
       </c>
       <c r="F92" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>19</v>
@@ -3045,13 +3048,13 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E93">
         <v>5328</v>
       </c>
       <c r="F93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>19</v>
@@ -3074,13 +3077,13 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E94">
         <v>5326</v>
       </c>
       <c r="F94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>19</v>
@@ -3103,13 +3106,13 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E95">
         <v>5319</v>
       </c>
       <c r="F95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>19</v>
@@ -3132,13 +3135,13 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E96">
         <v>5323</v>
       </c>
       <c r="F96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>19</v>
@@ -3161,13 +3164,13 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E97">
         <v>5347</v>
       </c>
       <c r="F97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>19</v>
@@ -3198,180 +3201,807 @@
       </c>
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H99" s="2"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="1"/>
+      <c r="D99" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99">
+        <v>5344</v>
+      </c>
+      <c r="F99" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99" s="2">
+        <v>0</v>
+      </c>
+      <c r="K99" s="1">
+        <v>46212.771064814813</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="1"/>
+      <c r="D100" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100">
+        <v>5341</v>
+      </c>
+      <c r="F100" t="s">
+        <v>50</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1">
+        <v>46212.771064814813</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H101" s="2"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="1"/>
+      <c r="D101" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101">
+        <v>5345</v>
+      </c>
+      <c r="F101" t="s">
+        <v>27</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101" s="2">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1">
+        <v>46212.77175925926</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H102" s="2"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="1"/>
+      <c r="D102" t="s">
+        <v>21</v>
+      </c>
+      <c r="E102">
+        <v>5336</v>
+      </c>
+      <c r="F102" t="s">
+        <v>30</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J102" s="2">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="K102" s="1">
+        <v>46212.772453703707</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H103" s="2"/>
       <c r="I103" s="1"/>
       <c r="J103" s="2"/>
       <c r="K103" s="1"/>
+      <c r="M103" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H104" s="2"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="1"/>
+      <c r="D104" t="s">
+        <v>21</v>
+      </c>
+      <c r="E104">
+        <v>5766</v>
+      </c>
+      <c r="F104" t="s">
+        <v>52</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104" s="2">
+        <v>0</v>
+      </c>
+      <c r="K104" s="1">
+        <v>46212.773148148146</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H105" s="2"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="1"/>
+      <c r="D105" t="s">
+        <v>21</v>
+      </c>
+      <c r="E105">
+        <v>5346</v>
+      </c>
+      <c r="F105" t="s">
+        <v>31</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105" s="2">
+        <v>0</v>
+      </c>
+      <c r="K105" s="1">
+        <v>46212.773148148146</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H106" s="2"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="1"/>
+      <c r="D106" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106">
+        <v>5320</v>
+      </c>
+      <c r="F106" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J106" s="2">
+        <v>0</v>
+      </c>
+      <c r="K106" s="1">
+        <v>46212.773842592593</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H107" s="2"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="1"/>
+      <c r="D107" t="s">
+        <v>21</v>
+      </c>
+      <c r="E107">
+        <v>5767</v>
+      </c>
+      <c r="F107" t="s">
+        <v>53</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J107" s="2">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1">
+        <v>46212.774537037039</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H108" s="2"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="1"/>
+      <c r="D108" t="s">
+        <v>21</v>
+      </c>
+      <c r="E108">
+        <v>5343</v>
+      </c>
+      <c r="F108" t="s">
+        <v>36</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J108" s="2">
+        <v>0</v>
+      </c>
+      <c r="K108" s="1">
+        <v>46212.775231481479</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H109" s="2"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="2"/>
-      <c r="K109" s="1"/>
+      <c r="D109" t="s">
+        <v>21</v>
+      </c>
+      <c r="E109">
+        <v>5322</v>
+      </c>
+      <c r="F109" t="s">
+        <v>38</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J109" s="2">
+        <v>5.9606481481481481E-3</v>
+      </c>
+      <c r="K109" s="1">
+        <v>46212.775925925926</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H110" s="2"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="2"/>
-      <c r="K110" s="1"/>
+      <c r="D110" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110">
+        <v>5330</v>
+      </c>
+      <c r="F110" t="s">
+        <v>35</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J110" s="2">
+        <v>6.4930555555555557E-3</v>
+      </c>
+      <c r="K110" s="1">
+        <v>46212.776620370372</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H111" s="2"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="1"/>
+      <c r="D111" t="s">
+        <v>21</v>
+      </c>
+      <c r="E111">
+        <v>5768</v>
+      </c>
+      <c r="F111" t="s">
+        <v>54</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J111" s="2">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1">
+        <v>46212.776620370372</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H112" s="2"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="2"/>
-      <c r="K112" s="1"/>
-    </row>
-    <row r="113" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H113" s="2"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="2"/>
-      <c r="K113" s="1"/>
-    </row>
-    <row r="114" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H114" s="2"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="1"/>
-    </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H115" s="2"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="2"/>
-      <c r="K115" s="1"/>
-    </row>
-    <row r="116" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H116" s="2"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="1"/>
-    </row>
-    <row r="117" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H117" s="2"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="2"/>
-      <c r="K117" s="1"/>
-    </row>
-    <row r="118" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H118" s="2"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="1"/>
-    </row>
-    <row r="119" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H119" s="2"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="2"/>
-      <c r="K119" s="1"/>
-    </row>
-    <row r="120" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H120" s="2"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="2"/>
-      <c r="K120" s="1"/>
-    </row>
-    <row r="121" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H121" s="2"/>
-      <c r="I121" s="1"/>
-      <c r="J121" s="2"/>
-      <c r="K121" s="1"/>
-    </row>
-    <row r="122" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H122" s="2"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="2"/>
-      <c r="K122" s="1"/>
-    </row>
-    <row r="123" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H123" s="2"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="2"/>
-      <c r="K123" s="1"/>
-    </row>
-    <row r="124" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H124" s="2"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="2"/>
-      <c r="K124" s="1"/>
-    </row>
-    <row r="125" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H125" s="2"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="2"/>
-      <c r="K125" s="1"/>
-    </row>
-    <row r="126" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H126" s="2"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="2"/>
-      <c r="K126" s="1"/>
-    </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D112" t="s">
+        <v>21</v>
+      </c>
+      <c r="E112">
+        <v>5340</v>
+      </c>
+      <c r="F112" t="s">
+        <v>39</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J112" s="2">
+        <v>0</v>
+      </c>
+      <c r="K112" s="1">
+        <v>46212.777314814812</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D113" t="s">
+        <v>21</v>
+      </c>
+      <c r="E113">
+        <v>5329</v>
+      </c>
+      <c r="F113" t="s">
+        <v>40</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J113" s="2">
+        <v>0</v>
+      </c>
+      <c r="K113" s="1">
+        <v>46212.778009259258</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D114" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114">
+        <v>5318</v>
+      </c>
+      <c r="F114" t="s">
+        <v>41</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J114" s="2">
+        <v>0</v>
+      </c>
+      <c r="K114" s="1">
+        <v>46212.778703703705</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D115" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115">
+        <v>5333</v>
+      </c>
+      <c r="F115" t="s">
+        <v>42</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J115" s="2">
+        <v>0</v>
+      </c>
+      <c r="K115" s="1">
+        <v>46212.779398148145</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D116" t="s">
+        <v>21</v>
+      </c>
+      <c r="E116">
+        <v>5338</v>
+      </c>
+      <c r="F116" t="s">
+        <v>49</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J116" s="2">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1">
+        <v>46212.752430555556</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D117" t="s">
+        <v>21</v>
+      </c>
+      <c r="E117">
+        <v>5335</v>
+      </c>
+      <c r="F117" t="s">
+        <v>46</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117" s="2">
+        <v>0</v>
+      </c>
+      <c r="K117" s="1">
+        <v>46212.753125000003</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D118" t="s">
+        <v>21</v>
+      </c>
+      <c r="E118">
+        <v>5321</v>
+      </c>
+      <c r="F118" t="s">
+        <v>25</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118" s="2">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1">
+        <v>46212.753819444442</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D119" t="s">
+        <v>21</v>
+      </c>
+      <c r="E119">
+        <v>5337</v>
+      </c>
+      <c r="F119" t="s">
+        <v>48</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J119" s="2">
+        <v>0</v>
+      </c>
+      <c r="K119" s="1">
+        <v>46212.754513888889</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D120" t="s">
+        <v>21</v>
+      </c>
+      <c r="E120">
+        <v>5334</v>
+      </c>
+      <c r="F120" t="s">
+        <v>45</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J120" s="2">
+        <v>0</v>
+      </c>
+      <c r="K120" s="1">
+        <v>46212.754513888889</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D121" t="s">
+        <v>21</v>
+      </c>
+      <c r="E121">
+        <v>5582</v>
+      </c>
+      <c r="F121" t="s">
+        <v>55</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J121" s="2">
+        <v>0</v>
+      </c>
+      <c r="K121" s="1">
+        <v>46212.755208333336</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D122" t="s">
+        <v>21</v>
+      </c>
+      <c r="E122">
+        <v>5328</v>
+      </c>
+      <c r="F122" t="s">
+        <v>34</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J122" s="2">
+        <v>0</v>
+      </c>
+      <c r="K122" s="1">
+        <v>46212.755902777775</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D123" t="s">
+        <v>21</v>
+      </c>
+      <c r="E123">
+        <v>5326</v>
+      </c>
+      <c r="F123" t="s">
+        <v>32</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" s="2">
+        <v>0</v>
+      </c>
+      <c r="K123" s="1">
+        <v>46212.756597222222</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D124" t="s">
+        <v>21</v>
+      </c>
+      <c r="E124">
+        <v>5319</v>
+      </c>
+      <c r="F124" t="s">
+        <v>23</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="2">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1">
+        <v>46212.757291666669</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D125" t="s">
+        <v>21</v>
+      </c>
+      <c r="E125">
+        <v>5323</v>
+      </c>
+      <c r="F125" t="s">
+        <v>28</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J125" s="2">
+        <v>0</v>
+      </c>
+      <c r="K125" s="1">
+        <v>46212.757986111108</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D126" t="s">
+        <v>21</v>
+      </c>
+      <c r="E126">
+        <v>5347</v>
+      </c>
+      <c r="F126" t="s">
+        <v>26</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J126" s="2">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="K126" s="1">
+        <v>46212.757986111108</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
-    </row>
-    <row r="128" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M127" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H128" s="2"/>
       <c r="I128" s="1"/>
       <c r="J128" s="2"/>
@@ -41086,7 +41716,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Reed-Beverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D011F8F-CAC4-43E9-941E-2B2A578649DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D646095-C9E9-484C-9C1C-D60F28241D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,10 +86,10 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
   </si>
   <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -580,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -749,7 +749,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="1"/>
       <c r="M6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
@@ -787,7 +787,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="1"/>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
@@ -854,7 +854,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="1"/>
       <c r="M11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
@@ -1008,7 +1008,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
       <c r="M17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
@@ -1104,7 +1104,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="1"/>
       <c r="M21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
@@ -1229,7 +1229,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1267,7 +1267,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="1"/>
       <c r="M28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
@@ -1421,7 +1421,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
       <c r="M34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
@@ -1749,7 +1749,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="1"/>
       <c r="M46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
@@ -2106,7 +2106,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="1"/>
       <c r="M59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
@@ -2410,7 +2410,7 @@
         <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2439,7 +2439,7 @@
         <v>24</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2468,7 +2468,7 @@
         <v>35</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2497,7 +2497,7 @@
         <v>46</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2608,7 +2608,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="1"/>
       <c r="M77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
@@ -3197,7 +3197,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="1"/>
       <c r="M98" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
@@ -3322,7 +3322,7 @@
       <c r="J103" s="2"/>
       <c r="K103" s="1"/>
       <c r="M103" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
@@ -3397,10 +3397,10 @@
         <v>20</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J106" s="2">
-        <v>0</v>
+        <v>5.6944444444444447E-3</v>
       </c>
       <c r="K106" s="1">
         <v>46212.773842592593</v>
@@ -3629,10 +3629,10 @@
         <v>20</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J114" s="2">
-        <v>0</v>
+        <v>1.0625000000000001E-2</v>
       </c>
       <c r="K114" s="1">
         <v>46212.778703703705</v>
@@ -3998,7 +3998,7 @@
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
       <c r="M127" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
@@ -11406,6 +11406,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -14729,6 +14730,7 @@
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1934" s="1"/>
+      <c r="J1934" s="2"/>
       <c r="K1934" s="1"/>
     </row>
     <row r="1935" spans="8:11" x14ac:dyDescent="0.3">
@@ -14739,14 +14741,17 @@
     <row r="1936" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
+      <c r="K1936" s="1"/>
     </row>
     <row r="1937" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
+      <c r="J1937" s="2"/>
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1938" s="1"/>
+      <c r="J1938" s="2"/>
       <c r="K1938" s="1"/>
     </row>
     <row r="1939" spans="8:11" x14ac:dyDescent="0.3">
@@ -14772,6 +14777,7 @@
     <row r="1943" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
+      <c r="J1943" s="2"/>
       <c r="K1943" s="1"/>
     </row>
     <row r="1944" spans="8:11" x14ac:dyDescent="0.3">
@@ -14781,9 +14787,11 @@
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
+      <c r="K1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1946" s="1"/>
+      <c r="J1946" s="2"/>
       <c r="K1946" s="1"/>
     </row>
     <row r="1947" spans="8:11" x14ac:dyDescent="0.3">
@@ -41721,6 +41729,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -41728,6 +41737,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -41735,6 +41745,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -41750,6 +41761,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -41759,6 +41771,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -41766,9 +41779,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -41776,12 +41795,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -41789,12 +41811,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -41806,9 +41831,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -41823,6 +41850,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -41849,6 +41877,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -41859,7 +41888,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -41867,6 +41901,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -41878,6 +41913,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -41885,6 +41921,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -41899,13 +41936,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -41916,15 +41959,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -41940,6 +41986,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -41958,6 +42005,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -41969,6 +42017,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -41986,18 +42035,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -42026,6 +42080,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -42033,9 +42088,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -42058,12 +42115,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -42078,9 +42138,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -42096,12 +42158,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -42122,6 +42186,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -42133,9 +42198,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -42147,6 +42214,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -42186,9 +42254,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -42196,9 +42266,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -42209,6 +42281,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -42216,18 +42289,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -42235,6 +42316,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -42245,6 +42327,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -42271,15 +42354,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -42301,6 +42388,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -42308,9 +42396,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -42318,6 +42408,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -42329,6 +42420,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -42343,6 +42435,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -42352,6 +42448,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -42363,6 +42460,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -42373,10 +42471,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -42384,6 +42487,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -42398,6 +42502,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -42420,6 +42525,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -42439,25 +42545,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -42465,6 +42583,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -42472,15 +42591,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -42494,6 +42620,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -42512,9 +42639,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -42522,9 +42651,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -42532,6 +42663,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -42548,10 +42680,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Reed-Beverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{524633DF-D28D-46EB-BF21-0DC331F6E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49A0CBD9-2351-4F1D-855E-2DC02A8775A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="64">
   <si>
     <t>Company Name</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Speed Mangement-C</t>
+  </si>
+  <si>
+    <t>Dangers of Distracted Driving</t>
   </si>
   <si>
     <t>Vehicle Inspection</t>
@@ -207,6 +210,27 @@
   </si>
   <si>
     <t>Salvador Herrera</t>
+  </si>
+  <si>
+    <t>Ali Hopson</t>
+  </si>
+  <si>
+    <t>Braiden Johnson</t>
+  </si>
+  <si>
+    <t>Chemmeyon Sneed</t>
+  </si>
+  <si>
+    <t>Isaac Lopez</t>
+  </si>
+  <si>
+    <t>Jawuan Thomas</t>
+  </si>
+  <si>
+    <t>Luis Archuleta</t>
+  </si>
+  <si>
+    <t>Michael Booker</t>
   </si>
 </sst>
 </file>
@@ -580,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -595,47 +619,47 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>5344</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -656,15 +680,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>5319</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -685,15 +709,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>5320</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -714,15 +738,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>5321</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -743,7 +767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
       <c r="J6" s="2"/>
@@ -751,15 +775,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>5347</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -780,7 +804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
       <c r="J8" s="2"/>
@@ -788,15 +812,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>5345</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -817,15 +841,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>5323</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -846,7 +870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2"/>
@@ -854,15 +878,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>5324</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -883,15 +907,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>5336</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -912,15 +936,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>5346</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -941,15 +965,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15">
         <v>5326</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -970,15 +994,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>5327</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -1009,13 +1033,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>5328</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -1038,13 +1062,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>5330</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -1067,13 +1091,13 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>5343</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -1104,13 +1128,13 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>5325</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -1133,13 +1157,13 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23">
         <v>5322</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -1162,13 +1186,13 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24">
         <v>5340</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -1191,13 +1215,13 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25">
         <v>5329</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -1228,13 +1252,13 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27">
         <v>5318</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -1265,13 +1289,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29">
         <v>5333</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -1294,13 +1318,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30">
         <v>5331</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -1323,13 +1347,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31">
         <v>5332</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -1352,13 +1376,13 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32">
         <v>5334</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -1381,13 +1405,13 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33">
         <v>5335</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -1418,13 +1442,13 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C35">
         <v>5339</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -1447,13 +1471,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C36">
         <v>5337</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -1476,13 +1500,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37">
         <v>5338</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -1505,13 +1529,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C38">
         <v>5341</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -1534,13 +1558,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C39">
         <v>5342</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -1563,13 +1587,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40">
         <v>5344</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F40" t="s">
         <v>17</v>
@@ -1592,13 +1616,13 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41">
         <v>5324</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
@@ -1621,13 +1645,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C42">
         <v>5341</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F42" t="s">
         <v>17</v>
@@ -1650,13 +1674,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C43">
         <v>5332</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
@@ -1679,13 +1703,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C44">
         <v>5345</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F44" t="s">
         <v>17</v>
@@ -1708,13 +1732,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C45">
         <v>5336</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
         <v>17</v>
@@ -1745,13 +1769,13 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C47">
         <v>5346</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
         <v>17</v>
@@ -1774,13 +1798,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C48">
         <v>5320</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
@@ -1803,13 +1827,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C49">
         <v>5343</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F49" t="s">
         <v>17</v>
@@ -1832,13 +1856,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C50">
         <v>5325</v>
       </c>
       <c r="D50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F50" t="s">
         <v>17</v>
@@ -1861,13 +1885,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C51">
         <v>5342</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F51" t="s">
         <v>17</v>
@@ -1890,13 +1914,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C52">
         <v>5322</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
@@ -1919,13 +1943,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C53">
         <v>5330</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53" t="s">
         <v>17</v>
@@ -1948,13 +1972,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C54">
         <v>5340</v>
       </c>
       <c r="D54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F54" t="s">
         <v>17</v>
@@ -1977,13 +2001,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C55">
         <v>5329</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F55" t="s">
         <v>17</v>
@@ -2006,13 +2030,13 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C56">
         <v>5318</v>
       </c>
       <c r="D56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F56" t="s">
         <v>17</v>
@@ -2035,13 +2059,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C57">
         <v>5333</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F57" t="s">
         <v>17</v>
@@ -2064,13 +2088,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C58">
         <v>5339</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F58" t="s">
         <v>17</v>
@@ -2101,13 +2125,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C60">
         <v>5338</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F60" t="s">
         <v>17</v>
@@ -2130,13 +2154,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C61">
         <v>5335</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F61" t="s">
         <v>17</v>
@@ -2159,13 +2183,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C62">
         <v>5321</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F62" t="s">
         <v>17</v>
@@ -2188,13 +2212,13 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C63">
         <v>5337</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
@@ -2217,13 +2241,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C64">
         <v>5334</v>
       </c>
       <c r="D64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F64" t="s">
         <v>17</v>
@@ -2246,13 +2270,13 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C65">
         <v>5328</v>
       </c>
       <c r="D65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F65" t="s">
         <v>17</v>
@@ -2275,13 +2299,13 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C66">
         <v>5326</v>
       </c>
       <c r="D66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F66" t="s">
         <v>17</v>
@@ -2304,13 +2328,13 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C67">
         <v>5319</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F67" t="s">
         <v>17</v>
@@ -2333,13 +2357,13 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C68">
         <v>5323</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
@@ -2362,13 +2386,13 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C69">
         <v>5347</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
@@ -2391,13 +2415,13 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C70">
         <v>5341</v>
       </c>
       <c r="D70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
@@ -2420,13 +2444,13 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C71">
         <v>5320</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -2449,13 +2473,13 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C72">
         <v>5330</v>
       </c>
       <c r="D72" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
@@ -2478,13 +2502,13 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C73">
         <v>5335</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
@@ -2507,13 +2531,13 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C74">
         <v>5344</v>
       </c>
       <c r="D74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F74" t="s">
         <v>19</v>
@@ -2536,13 +2560,13 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C75">
         <v>5345</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F75" t="s">
         <v>19</v>
@@ -2565,13 +2589,13 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C76">
         <v>5336</v>
       </c>
       <c r="D76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F76" t="s">
         <v>19</v>
@@ -2602,13 +2626,13 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C78">
         <v>5766</v>
       </c>
       <c r="D78" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F78" t="s">
         <v>19</v>
@@ -2631,13 +2655,13 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C79">
         <v>5346</v>
       </c>
       <c r="D79" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F79" t="s">
         <v>19</v>
@@ -2660,13 +2684,13 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C80">
         <v>5767</v>
       </c>
       <c r="D80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F80" t="s">
         <v>19</v>
@@ -2689,13 +2713,13 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C81">
         <v>5343</v>
       </c>
       <c r="D81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F81" t="s">
         <v>19</v>
@@ -2718,13 +2742,13 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C82">
         <v>5322</v>
       </c>
       <c r="D82" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
@@ -2747,13 +2771,13 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C83">
         <v>5768</v>
       </c>
       <c r="D83" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F83" t="s">
         <v>19</v>
@@ -2776,13 +2800,13 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C84">
         <v>5340</v>
       </c>
       <c r="D84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
@@ -2805,13 +2829,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C85">
         <v>5329</v>
       </c>
       <c r="D85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F85" t="s">
         <v>19</v>
@@ -2834,13 +2858,13 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C86">
         <v>5318</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F86" t="s">
         <v>19</v>
@@ -2863,13 +2887,13 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C87">
         <v>5333</v>
       </c>
       <c r="D87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F87" t="s">
         <v>19</v>
@@ -2892,13 +2916,13 @@
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C88">
         <v>5338</v>
       </c>
       <c r="D88" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F88" t="s">
         <v>19</v>
@@ -2921,13 +2945,13 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C89">
         <v>5321</v>
       </c>
       <c r="D89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F89" t="s">
         <v>19</v>
@@ -2950,13 +2974,13 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C90">
         <v>5337</v>
       </c>
       <c r="D90" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2979,13 +3003,13 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C91">
         <v>5334</v>
       </c>
       <c r="D91" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F91" t="s">
         <v>19</v>
@@ -3008,13 +3032,13 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C92">
         <v>5582</v>
       </c>
       <c r="D92" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -3037,13 +3061,13 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C93">
         <v>5328</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -3066,13 +3090,13 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C94">
         <v>5326</v>
       </c>
       <c r="D94" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -3095,13 +3119,13 @@
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C95">
         <v>5319</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -3124,13 +3148,13 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C96">
         <v>5323</v>
       </c>
       <c r="D96" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -3153,13 +3177,13 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C97">
         <v>5347</v>
       </c>
       <c r="D97" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -3190,16 +3214,16 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C99">
         <v>5344</v>
       </c>
       <c r="D99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G99" t="s">
         <v>12</v>
@@ -3227,16 +3251,16 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C101">
         <v>5341</v>
       </c>
       <c r="D101" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G101" t="s">
         <v>10</v>
@@ -3256,16 +3280,16 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C102">
         <v>5345</v>
       </c>
       <c r="D102" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G102" t="s">
         <v>10</v>
@@ -3285,16 +3309,16 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C103">
         <v>5336</v>
       </c>
       <c r="D103" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G103" t="s">
         <v>12</v>
@@ -3322,16 +3346,16 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C105">
         <v>5766</v>
       </c>
       <c r="D105" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G105" t="s">
         <v>10</v>
@@ -3351,16 +3375,16 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C106">
         <v>5346</v>
       </c>
       <c r="D106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G106" t="s">
         <v>13</v>
@@ -3380,16 +3404,16 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C107">
         <v>5320</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -3409,16 +3433,16 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C108">
         <v>5767</v>
       </c>
       <c r="D108" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G108" t="s">
         <v>13</v>
@@ -3438,16 +3462,16 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C109">
         <v>5343</v>
       </c>
       <c r="D109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G109" t="s">
         <v>13</v>
@@ -3467,16 +3491,16 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C110">
         <v>5322</v>
       </c>
       <c r="D110" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G110" t="s">
         <v>10</v>
@@ -3496,16 +3520,16 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C111">
         <v>5330</v>
       </c>
       <c r="D111" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G111" t="s">
         <v>10</v>
@@ -3525,16 +3549,16 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C112">
         <v>5768</v>
       </c>
       <c r="D112" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F112" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G112" t="s">
         <v>13</v>
@@ -3554,16 +3578,16 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C113">
         <v>5340</v>
       </c>
       <c r="D113" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G113" t="s">
         <v>13</v>
@@ -3583,16 +3607,16 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C114">
         <v>5329</v>
       </c>
       <c r="D114" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F114" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G114" t="s">
         <v>12</v>
@@ -3620,16 +3644,16 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C116">
         <v>5318</v>
       </c>
       <c r="D116" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G116" t="s">
         <v>10</v>
@@ -3649,16 +3673,16 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C117">
         <v>5333</v>
       </c>
       <c r="D117" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F117" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G117" t="s">
         <v>10</v>
@@ -3678,16 +3702,16 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C118">
         <v>5338</v>
       </c>
       <c r="D118" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G118" t="s">
         <v>13</v>
@@ -3707,16 +3731,16 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C119">
         <v>5335</v>
       </c>
       <c r="D119" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G119" t="s">
         <v>10</v>
@@ -3736,16 +3760,16 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C120">
         <v>5321</v>
       </c>
       <c r="D120" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G120" t="s">
         <v>13</v>
@@ -3765,16 +3789,16 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C121">
         <v>5337</v>
       </c>
       <c r="D121" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G121" t="s">
         <v>12</v>
@@ -3802,16 +3826,16 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C123">
         <v>5334</v>
       </c>
       <c r="D123" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F123" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G123" t="s">
         <v>10</v>
@@ -3831,16 +3855,16 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C124">
         <v>5582</v>
       </c>
       <c r="D124" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F124" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G124" t="s">
         <v>13</v>
@@ -3860,16 +3884,16 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C125">
         <v>5328</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G125" t="s">
         <v>13</v>
@@ -3889,16 +3913,16 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C126">
         <v>5326</v>
       </c>
       <c r="D126" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F126" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G126" t="s">
         <v>13</v>
@@ -3918,16 +3942,16 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C127">
         <v>5319</v>
       </c>
       <c r="D127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G127" t="s">
         <v>12</v>
@@ -3955,16 +3979,16 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C129">
         <v>5323</v>
       </c>
       <c r="D129" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G129" t="s">
         <v>14</v>
@@ -3992,16 +4016,16 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C131">
         <v>5347</v>
       </c>
       <c r="D131" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F131" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G131" t="s">
         <v>10</v>
@@ -4020,270 +4044,968 @@
       </c>
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H132" s="2"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="1"/>
+      <c r="B132" t="s">
+        <v>22</v>
+      </c>
+      <c r="C132">
+        <v>5344</v>
+      </c>
+      <c r="D132" t="s">
+        <v>23</v>
+      </c>
+      <c r="F132" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" s="2">
+        <v>6.6782407407407407E-3</v>
+      </c>
+      <c r="I132" s="1">
+        <v>46237.84884259259</v>
+      </c>
+      <c r="J132" s="2">
+        <v>0</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H133" s="2"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="2"/>
-      <c r="K133" s="1"/>
+      <c r="B133" t="s">
+        <v>22</v>
+      </c>
+      <c r="C133">
+        <v>5986</v>
+      </c>
+      <c r="D133" t="s">
+        <v>57</v>
+      </c>
+      <c r="F133" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" s="2">
+        <v>0</v>
+      </c>
+      <c r="I133" s="1">
+        <v>46237.849537037036</v>
+      </c>
+      <c r="J133" s="2">
+        <v>0</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H134" s="2"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="2"/>
-      <c r="K134" s="1"/>
+      <c r="B134" t="s">
+        <v>22</v>
+      </c>
+      <c r="C134">
+        <v>5341</v>
+      </c>
+      <c r="D134" t="s">
+        <v>51</v>
+      </c>
+      <c r="F134" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" t="s">
+        <v>10</v>
+      </c>
+      <c r="H134" s="2">
+        <v>8.1018518518518514E-3</v>
+      </c>
+      <c r="I134" s="1">
+        <v>46237.850231481483</v>
+      </c>
+      <c r="J134" s="2">
+        <v>0</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H135" s="2"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="2"/>
-      <c r="K135" s="1"/>
+      <c r="B135" t="s">
+        <v>22</v>
+      </c>
+      <c r="C135">
+        <v>5983</v>
+      </c>
+      <c r="D135" t="s">
+        <v>58</v>
+      </c>
+      <c r="F135" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" s="2">
+        <v>0</v>
+      </c>
+      <c r="I135" s="1">
+        <v>46237.850231481483</v>
+      </c>
+      <c r="J135" s="2">
+        <v>0</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H136" s="2"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="2"/>
-      <c r="K136" s="1"/>
+      <c r="B136" t="s">
+        <v>22</v>
+      </c>
+      <c r="C136">
+        <v>5985</v>
+      </c>
+      <c r="D136" t="s">
+        <v>59</v>
+      </c>
+      <c r="F136" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" s="2">
+        <v>0</v>
+      </c>
+      <c r="I136" s="1">
+        <v>46237.850925925923</v>
+      </c>
+      <c r="J136" s="2">
+        <v>0</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H137" s="2"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="2"/>
-      <c r="K137" s="1"/>
+      <c r="B137" t="s">
+        <v>22</v>
+      </c>
+      <c r="C137">
+        <v>5345</v>
+      </c>
+      <c r="D137" t="s">
+        <v>28</v>
+      </c>
+      <c r="F137" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" t="s">
+        <v>12</v>
+      </c>
+      <c r="H137" s="2">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="I137" s="1">
+        <v>46237.850925925923</v>
+      </c>
+      <c r="J137" s="2">
+        <v>0</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H138" s="2"/>
       <c r="I138" s="1"/>
       <c r="J138" s="2"/>
-      <c r="K138" s="1"/>
+      <c r="K138" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H139" s="2"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="2"/>
-      <c r="K139" s="1"/>
+      <c r="B139" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139">
+        <v>5766</v>
+      </c>
+      <c r="D139" t="s">
+        <v>53</v>
+      </c>
+      <c r="F139" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" s="2">
+        <v>0</v>
+      </c>
+      <c r="I139" s="1">
+        <v>46237.851620370369</v>
+      </c>
+      <c r="J139" s="2">
+        <v>0</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H140" s="2"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="2"/>
-      <c r="K140" s="1"/>
+      <c r="B140" t="s">
+        <v>22</v>
+      </c>
+      <c r="C140">
+        <v>5346</v>
+      </c>
+      <c r="D140" t="s">
+        <v>32</v>
+      </c>
+      <c r="F140" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" t="s">
+        <v>13</v>
+      </c>
+      <c r="H140" s="2">
+        <v>0</v>
+      </c>
+      <c r="I140" s="1">
+        <v>46237.852314814816</v>
+      </c>
+      <c r="J140" s="2">
+        <v>0</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H141" s="2"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="2"/>
-      <c r="K141" s="1"/>
+      <c r="B141" t="s">
+        <v>22</v>
+      </c>
+      <c r="C141">
+        <v>5320</v>
+      </c>
+      <c r="D141" t="s">
+        <v>25</v>
+      </c>
+      <c r="F141" t="s">
+        <v>20</v>
+      </c>
+      <c r="G141" t="s">
+        <v>10</v>
+      </c>
+      <c r="H141" s="2">
+        <v>6.145833333333333E-3</v>
+      </c>
+      <c r="I141" s="1">
+        <v>46237.853009259263</v>
+      </c>
+      <c r="J141" s="2">
+        <v>0</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H142" s="2"/>
-      <c r="I142" s="1"/>
-      <c r="J142" s="2"/>
-      <c r="K142" s="1"/>
+      <c r="B142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142">
+        <v>5767</v>
+      </c>
+      <c r="D142" t="s">
+        <v>54</v>
+      </c>
+      <c r="F142" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" t="s">
+        <v>13</v>
+      </c>
+      <c r="H142" s="2">
+        <v>0</v>
+      </c>
+      <c r="I142" s="1">
+        <v>46237.853009259263</v>
+      </c>
+      <c r="J142" s="2">
+        <v>0</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H143" s="2"/>
-      <c r="I143" s="1"/>
-      <c r="J143" s="2"/>
-      <c r="K143" s="1"/>
+      <c r="B143" t="s">
+        <v>22</v>
+      </c>
+      <c r="C143">
+        <v>5551</v>
+      </c>
+      <c r="D143" t="s">
+        <v>60</v>
+      </c>
+      <c r="F143" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" t="s">
+        <v>13</v>
+      </c>
+      <c r="H143" s="2">
+        <v>0</v>
+      </c>
+      <c r="I143" s="1">
+        <v>46237.853703703702</v>
+      </c>
+      <c r="J143" s="2">
+        <v>0</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H144" s="2"/>
-      <c r="I144" s="1"/>
-      <c r="J144" s="2"/>
-      <c r="K144" s="1"/>
-    </row>
-    <row r="145" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H145" s="2"/>
-      <c r="I145" s="1"/>
-      <c r="J145" s="2"/>
-      <c r="K145" s="1"/>
-    </row>
-    <row r="146" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H146" s="2"/>
-      <c r="I146" s="1"/>
-      <c r="J146" s="2"/>
-      <c r="K146" s="1"/>
-    </row>
-    <row r="147" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H147" s="2"/>
-      <c r="I147" s="1"/>
-      <c r="J147" s="2"/>
-      <c r="K147" s="1"/>
-    </row>
-    <row r="148" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H148" s="2"/>
-      <c r="I148" s="1"/>
-      <c r="J148" s="2"/>
-      <c r="K148" s="1"/>
-    </row>
-    <row r="149" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H149" s="2"/>
-      <c r="I149" s="1"/>
-      <c r="J149" s="2"/>
-      <c r="K149" s="1"/>
-    </row>
-    <row r="150" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H150" s="2"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="2"/>
-      <c r="K150" s="1"/>
-    </row>
-    <row r="151" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H151" s="2"/>
-      <c r="I151" s="1"/>
-      <c r="J151" s="2"/>
-      <c r="K151" s="1"/>
-    </row>
-    <row r="152" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H152" s="2"/>
-      <c r="I152" s="1"/>
-      <c r="J152" s="2"/>
-      <c r="K152" s="1"/>
-    </row>
-    <row r="153" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>22</v>
+      </c>
+      <c r="C144">
+        <v>5325</v>
+      </c>
+      <c r="D144" t="s">
+        <v>38</v>
+      </c>
+      <c r="F144" t="s">
+        <v>20</v>
+      </c>
+      <c r="G144" t="s">
+        <v>13</v>
+      </c>
+      <c r="H144" s="2">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>46237.853703703702</v>
+      </c>
+      <c r="J144" s="2">
+        <v>0</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>22</v>
+      </c>
+      <c r="C145">
+        <v>5987</v>
+      </c>
+      <c r="D145" t="s">
+        <v>61</v>
+      </c>
+      <c r="F145" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" t="s">
+        <v>10</v>
+      </c>
+      <c r="H145" s="2">
+        <v>9.780092592592592E-3</v>
+      </c>
+      <c r="I145" s="1">
+        <v>46237.854398148149</v>
+      </c>
+      <c r="J145" s="2">
+        <v>0</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>22</v>
+      </c>
+      <c r="C146">
+        <v>5322</v>
+      </c>
+      <c r="D146" t="s">
+        <v>39</v>
+      </c>
+      <c r="F146" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" t="s">
+        <v>13</v>
+      </c>
+      <c r="H146" s="2">
+        <v>0</v>
+      </c>
+      <c r="I146" s="1">
+        <v>46237.855092592596</v>
+      </c>
+      <c r="J146" s="2">
+        <v>0</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>22</v>
+      </c>
+      <c r="C147">
+        <v>5330</v>
+      </c>
+      <c r="D147" t="s">
+        <v>36</v>
+      </c>
+      <c r="F147" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" t="s">
+        <v>10</v>
+      </c>
+      <c r="H147" s="2">
+        <v>6.4351851851851853E-3</v>
+      </c>
+      <c r="I147" s="1">
+        <v>46237.855092592596</v>
+      </c>
+      <c r="J147" s="2">
+        <v>0</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>22</v>
+      </c>
+      <c r="C148">
+        <v>5340</v>
+      </c>
+      <c r="D148" t="s">
+        <v>40</v>
+      </c>
+      <c r="F148" t="s">
+        <v>20</v>
+      </c>
+      <c r="G148" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" s="2">
+        <v>0</v>
+      </c>
+      <c r="I148" s="1">
+        <v>46237.855787037035</v>
+      </c>
+      <c r="J148" s="2">
+        <v>0</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>22</v>
+      </c>
+      <c r="C149">
+        <v>5329</v>
+      </c>
+      <c r="D149" t="s">
+        <v>41</v>
+      </c>
+      <c r="F149" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" t="s">
+        <v>13</v>
+      </c>
+      <c r="H149" s="2">
+        <v>0</v>
+      </c>
+      <c r="I149" s="1">
+        <v>46237.856481481482</v>
+      </c>
+      <c r="J149" s="2">
+        <v>0</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>22</v>
+      </c>
+      <c r="C150">
+        <v>5318</v>
+      </c>
+      <c r="D150" t="s">
+        <v>42</v>
+      </c>
+      <c r="F150" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" t="s">
+        <v>13</v>
+      </c>
+      <c r="H150" s="2">
+        <v>0</v>
+      </c>
+      <c r="I150" s="1">
+        <v>46237.856481481482</v>
+      </c>
+      <c r="J150" s="2">
+        <v>0</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>22</v>
+      </c>
+      <c r="C151">
+        <v>5333</v>
+      </c>
+      <c r="D151" t="s">
+        <v>43</v>
+      </c>
+      <c r="F151" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" t="s">
+        <v>10</v>
+      </c>
+      <c r="H151" s="2">
+        <v>6.7361111111111111E-3</v>
+      </c>
+      <c r="I151" s="1">
+        <v>46237.857175925928</v>
+      </c>
+      <c r="J151" s="2">
+        <v>0</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>22</v>
+      </c>
+      <c r="C152">
+        <v>5984</v>
+      </c>
+      <c r="D152" t="s">
+        <v>62</v>
+      </c>
+      <c r="F152" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" t="s">
+        <v>12</v>
+      </c>
+      <c r="H152" s="2">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="I152" s="1">
+        <v>46237.857870370368</v>
+      </c>
+      <c r="J152" s="2">
+        <v>0</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H153" s="2"/>
       <c r="I153" s="1"/>
       <c r="J153" s="2"/>
-      <c r="K153" s="1"/>
-    </row>
-    <row r="154" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H154" s="2"/>
-      <c r="I154" s="1"/>
-      <c r="J154" s="2"/>
-      <c r="K154" s="1"/>
-    </row>
-    <row r="155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H155" s="2"/>
-      <c r="I155" s="1"/>
-      <c r="J155" s="2"/>
-      <c r="K155" s="1"/>
-    </row>
-    <row r="156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H156" s="2"/>
-      <c r="I156" s="1"/>
-      <c r="J156" s="2"/>
-      <c r="K156" s="1"/>
-    </row>
-    <row r="157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H157" s="2"/>
-      <c r="I157" s="1"/>
-      <c r="J157" s="2"/>
-      <c r="K157" s="1"/>
-    </row>
-    <row r="158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H158" s="2"/>
-      <c r="I158" s="1"/>
-      <c r="J158" s="2"/>
-      <c r="K158" s="1"/>
-    </row>
-    <row r="159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H159" s="2"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="2"/>
-      <c r="K159" s="1"/>
-    </row>
-    <row r="160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H160" s="2"/>
-      <c r="I160" s="1"/>
-      <c r="J160" s="2"/>
-      <c r="K160" s="1"/>
-    </row>
-    <row r="161" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H161" s="2"/>
-      <c r="I161" s="1"/>
-      <c r="J161" s="2"/>
-      <c r="K161" s="1"/>
-    </row>
-    <row r="162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H162" s="2"/>
-      <c r="I162" s="1"/>
-      <c r="J162" s="2"/>
-      <c r="K162" s="1"/>
-    </row>
-    <row r="163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K153" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>22</v>
+      </c>
+      <c r="C154">
+        <v>6024</v>
+      </c>
+      <c r="D154" t="s">
+        <v>63</v>
+      </c>
+      <c r="F154" t="s">
+        <v>20</v>
+      </c>
+      <c r="G154" t="s">
+        <v>13</v>
+      </c>
+      <c r="H154" s="2">
+        <v>0</v>
+      </c>
+      <c r="I154" s="1">
+        <v>46237.857870370368</v>
+      </c>
+      <c r="J154" s="2">
+        <v>0</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155">
+        <v>5335</v>
+      </c>
+      <c r="D155" t="s">
+        <v>47</v>
+      </c>
+      <c r="F155" t="s">
+        <v>20</v>
+      </c>
+      <c r="G155" t="s">
+        <v>10</v>
+      </c>
+      <c r="H155" s="2">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="I155" s="1">
+        <v>46237.835763888892</v>
+      </c>
+      <c r="J155" s="2">
+        <v>0</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156">
+        <v>5321</v>
+      </c>
+      <c r="D156" t="s">
+        <v>26</v>
+      </c>
+      <c r="F156" t="s">
+        <v>20</v>
+      </c>
+      <c r="G156" t="s">
+        <v>13</v>
+      </c>
+      <c r="H156" s="2">
+        <v>0</v>
+      </c>
+      <c r="I156" s="1">
+        <v>46237.836458333331</v>
+      </c>
+      <c r="J156" s="2">
+        <v>0</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>22</v>
+      </c>
+      <c r="C157">
+        <v>5337</v>
+      </c>
+      <c r="D157" t="s">
+        <v>49</v>
+      </c>
+      <c r="F157" t="s">
+        <v>20</v>
+      </c>
+      <c r="G157" t="s">
+        <v>13</v>
+      </c>
+      <c r="H157" s="2">
+        <v>0</v>
+      </c>
+      <c r="I157" s="1">
+        <v>46237.836458333331</v>
+      </c>
+      <c r="J157" s="2">
+        <v>0</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>22</v>
+      </c>
+      <c r="C158">
+        <v>5334</v>
+      </c>
+      <c r="D158" t="s">
+        <v>46</v>
+      </c>
+      <c r="F158" t="s">
+        <v>20</v>
+      </c>
+      <c r="G158" t="s">
+        <v>13</v>
+      </c>
+      <c r="H158" s="2">
+        <v>0</v>
+      </c>
+      <c r="I158" s="1">
+        <v>46237.837152777778</v>
+      </c>
+      <c r="J158" s="2">
+        <v>0</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>22</v>
+      </c>
+      <c r="C159">
+        <v>5582</v>
+      </c>
+      <c r="D159" t="s">
+        <v>56</v>
+      </c>
+      <c r="F159" t="s">
+        <v>20</v>
+      </c>
+      <c r="G159" t="s">
+        <v>13</v>
+      </c>
+      <c r="H159" s="2">
+        <v>0</v>
+      </c>
+      <c r="I159" s="1">
+        <v>46237.837847222225</v>
+      </c>
+      <c r="J159" s="2">
+        <v>0</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>22</v>
+      </c>
+      <c r="C160">
+        <v>5328</v>
+      </c>
+      <c r="D160" t="s">
+        <v>35</v>
+      </c>
+      <c r="F160" t="s">
+        <v>20</v>
+      </c>
+      <c r="G160" t="s">
+        <v>13</v>
+      </c>
+      <c r="H160" s="2">
+        <v>0</v>
+      </c>
+      <c r="I160" s="1">
+        <v>46237.838541666664</v>
+      </c>
+      <c r="J160" s="2">
+        <v>0</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>22</v>
+      </c>
+      <c r="C161">
+        <v>5326</v>
+      </c>
+      <c r="D161" t="s">
+        <v>33</v>
+      </c>
+      <c r="F161" t="s">
+        <v>20</v>
+      </c>
+      <c r="G161" t="s">
+        <v>13</v>
+      </c>
+      <c r="H161" s="2">
+        <v>0</v>
+      </c>
+      <c r="I161" s="1">
+        <v>46237.838541666664</v>
+      </c>
+      <c r="J161" s="2">
+        <v>0</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>22</v>
+      </c>
+      <c r="C162">
+        <v>5319</v>
+      </c>
+      <c r="D162" t="s">
+        <v>24</v>
+      </c>
+      <c r="F162" t="s">
+        <v>20</v>
+      </c>
+      <c r="G162" t="s">
+        <v>12</v>
+      </c>
+      <c r="H162" s="2">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="I162" s="1">
+        <v>46237.839236111111</v>
+      </c>
+      <c r="J162" s="2">
+        <v>0</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H163" s="2"/>
       <c r="I163" s="1"/>
       <c r="J163" s="2"/>
-      <c r="K163" s="1"/>
-    </row>
-    <row r="164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H164" s="2"/>
-      <c r="I164" s="1"/>
-      <c r="J164" s="2"/>
-      <c r="K164" s="1"/>
-    </row>
-    <row r="165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K163" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>22</v>
+      </c>
+      <c r="C164">
+        <v>5347</v>
+      </c>
+      <c r="D164" t="s">
+        <v>27</v>
+      </c>
+      <c r="F164" t="s">
+        <v>20</v>
+      </c>
+      <c r="G164" t="s">
+        <v>12</v>
+      </c>
+      <c r="H164" s="2">
+        <v>1.25E-3</v>
+      </c>
+      <c r="I164" s="1">
+        <v>46237.839930555558</v>
+      </c>
+      <c r="J164" s="2">
+        <v>0</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H165" s="2"/>
       <c r="I165" s="1"/>
       <c r="J165" s="2"/>
-      <c r="K165" s="1"/>
-    </row>
-    <row r="166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K165" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H166" s="2"/>
       <c r="I166" s="1"/>
       <c r="J166" s="2"/>
       <c r="K166" s="1"/>
     </row>
-    <row r="167" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H167" s="2"/>
       <c r="I167" s="1"/>
       <c r="J167" s="2"/>
       <c r="K167" s="1"/>
     </row>
-    <row r="168" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H168" s="2"/>
       <c r="I168" s="1"/>
       <c r="J168" s="2"/>
       <c r="K168" s="1"/>
     </row>
-    <row r="169" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H169" s="2"/>
       <c r="I169" s="1"/>
       <c r="J169" s="2"/>
       <c r="K169" s="1"/>
     </row>
-    <row r="170" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H170" s="2"/>
       <c r="I170" s="1"/>
       <c r="J170" s="2"/>
       <c r="K170" s="1"/>
     </row>
-    <row r="171" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H171" s="2"/>
       <c r="I171" s="1"/>
       <c r="J171" s="2"/>
       <c r="K171" s="1"/>
     </row>
-    <row r="172" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H172" s="2"/>
       <c r="I172" s="1"/>
       <c r="J172" s="2"/>
       <c r="K172" s="1"/>
     </row>
-    <row r="173" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H173" s="2"/>
       <c r="I173" s="1"/>
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
       <c r="K174" s="1"/>
     </row>
-    <row r="175" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H175" s="2"/>
       <c r="I175" s="1"/>
       <c r="J175" s="2"/>
       <c r="K175" s="1"/>
     </row>
-    <row r="176" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H176" s="2"/>
       <c r="I176" s="1"/>
       <c r="J176" s="2"/>
@@ -14867,9 +15589,11 @@
       <c r="K1944" s="1"/>
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1945" s="2"/>
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1946" s="2"/>
       <c r="I1946" s="1"/>
       <c r="K1946" s="1"/>
     </row>
@@ -14935,6 +15659,7 @@
       <c r="K1958" s="1"/>
     </row>
     <row r="1959" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1959" s="2"/>
       <c r="I1959" s="1"/>
       <c r="K1959" s="1"/>
     </row>
@@ -14977,6 +15702,7 @@
       <c r="K1966" s="1"/>
     </row>
     <row r="1967" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1967" s="2"/>
       <c r="I1967" s="1"/>
     </row>
     <row r="1968" spans="8:11" x14ac:dyDescent="0.25">
@@ -14990,6 +15716,7 @@
       <c r="I1969" s="1"/>
     </row>
     <row r="1970" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1970" s="2"/>
       <c r="I1970" s="1"/>
       <c r="K1970" s="1"/>
     </row>
@@ -15060,6 +15787,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -15089,6 +15817,7 @@
       <c r="K1988" s="1"/>
     </row>
     <row r="1989" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1989" s="2"/>
       <c r="I1989" s="1"/>
       <c r="K1989" s="1"/>
     </row>
@@ -15110,6 +15839,7 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -15188,6 +15918,7 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -45369,6 +46100,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -45383,11 +46115,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -45398,10 +46132,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -45419,14 +46156,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -45437,14 +46177,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -45471,6 +46214,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -45479,6 +46223,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -45491,22 +46236,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -45525,6 +46275,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -45535,10 +46286,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -45547,10 +46300,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -45564,82 +46319,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -45653,6 +46423,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -45663,6 +46434,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -45670,6 +46442,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -45678,86 +46451,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -45774,26 +46560,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -45824,6 +46616,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -45833,10 +46626,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -45849,14 +46644,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -45865,14 +46663,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -45891,26 +46692,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -45929,6 +46736,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -45937,10 +46745,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -45949,6 +46759,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -45961,10 +46772,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -45973,6 +46786,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -45981,14 +46795,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -45997,14 +46814,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -46021,76 +46841,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -46104,31 +46933,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -46141,10 +46977,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -46153,10 +46991,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -46165,6 +47005,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -46179,10 +47020,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -46191,10 +47034,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -46208,6 +47053,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -46223,14 +47069,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -46248,14 +47097,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -46268,10 +47120,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -46280,14 +47134,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -46296,10 +47153,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -46308,14 +47167,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -46337,6 +47199,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -46345,39 +47208,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Reed-Beverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49A0CBD9-2351-4F1D-855E-2DC02A8775A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63E93BFE-4D33-4751-B334-5E1C156FFD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="64">
   <si>
     <t>Company Name</t>
   </si>
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -812,7 +812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>22</v>
       </c>
@@ -907,7 +907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1374,7 +1374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>22</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>22</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>22</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>22</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>22</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>22</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>22</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -3925,10 +3925,10 @@
         <v>21</v>
       </c>
       <c r="G126" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H126" s="2">
-        <v>0</v>
+        <v>5.4050925925925924E-3</v>
       </c>
       <c r="I126" s="1">
         <v>46212.756597222222</v>
@@ -3940,7 +3940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>22</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>12</v>
       </c>
       <c r="H127" s="2">
-        <v>7.6388888888888893E-4</v>
+        <v>8.2175925925925927E-4</v>
       </c>
       <c r="I127" s="1">
         <v>46212.757291666669</v>
@@ -4095,7 +4095,7 @@
         <v>46237.849537037036</v>
       </c>
       <c r="J133" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K133" s="1" t="s">
         <v>11</v>
@@ -4153,7 +4153,7 @@
         <v>46237.850231481483</v>
       </c>
       <c r="J135" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K135" s="1" t="s">
         <v>11</v>
@@ -4182,7 +4182,7 @@
         <v>46237.850925925923</v>
       </c>
       <c r="J136" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K136" s="1" t="s">
         <v>11</v>
@@ -4211,7 +4211,7 @@
         <v>46237.850925925923</v>
       </c>
       <c r="J137" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K137" s="1" t="s">
         <v>11</v>
@@ -4239,16 +4239,16 @@
         <v>20</v>
       </c>
       <c r="G139" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H139" s="2">
-        <v>0</v>
+        <v>8.0208333333333329E-3</v>
       </c>
       <c r="I139" s="1">
         <v>46237.851620370369</v>
       </c>
       <c r="J139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" s="1" t="s">
         <v>11</v>
@@ -4277,7 +4277,7 @@
         <v>46237.852314814816</v>
       </c>
       <c r="J140" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>11</v>
@@ -4335,7 +4335,7 @@
         <v>46237.853009259263</v>
       </c>
       <c r="J142" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>11</v>
@@ -4364,7 +4364,7 @@
         <v>46237.853703703702</v>
       </c>
       <c r="J143" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K143" s="1" t="s">
         <v>11</v>
@@ -4393,7 +4393,7 @@
         <v>46237.853703703702</v>
       </c>
       <c r="J144" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>11</v>
@@ -4442,16 +4442,16 @@
         <v>20</v>
       </c>
       <c r="G146" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H146" s="2">
-        <v>0</v>
+        <v>5.5902777777777773E-3</v>
       </c>
       <c r="I146" s="1">
         <v>46237.855092592596</v>
       </c>
       <c r="J146" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>11</v>
@@ -4509,7 +4509,7 @@
         <v>46237.855787037035</v>
       </c>
       <c r="J148" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K148" s="1" t="s">
         <v>11</v>
@@ -4538,7 +4538,7 @@
         <v>46237.856481481482</v>
       </c>
       <c r="J149" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>11</v>
@@ -4558,16 +4558,16 @@
         <v>20</v>
       </c>
       <c r="G150" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H150" s="2">
-        <v>0</v>
+        <v>7.858796296296296E-3</v>
       </c>
       <c r="I150" s="1">
         <v>46237.856481481482</v>
       </c>
       <c r="J150" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K150" s="1" t="s">
         <v>11</v>
@@ -4625,7 +4625,7 @@
         <v>46237.857870370368</v>
       </c>
       <c r="J152" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>11</v>
@@ -4662,7 +4662,7 @@
         <v>46237.857870370368</v>
       </c>
       <c r="J154" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K154" s="1" t="s">
         <v>11</v>
@@ -4720,7 +4720,7 @@
         <v>46237.836458333331</v>
       </c>
       <c r="J156" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K156" s="1" t="s">
         <v>11</v>
@@ -4749,7 +4749,7 @@
         <v>46237.836458333331</v>
       </c>
       <c r="J157" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>11</v>
@@ -4778,7 +4778,7 @@
         <v>46237.837152777778</v>
       </c>
       <c r="J158" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>11</v>
@@ -4807,7 +4807,7 @@
         <v>46237.837847222225</v>
       </c>
       <c r="J159" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>11</v>
@@ -4836,7 +4836,7 @@
         <v>46237.838541666664</v>
       </c>
       <c r="J160" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>11</v>
@@ -4856,16 +4856,16 @@
         <v>20</v>
       </c>
       <c r="G161" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H161" s="2">
-        <v>0</v>
+        <v>5.9490740740740745E-3</v>
       </c>
       <c r="I161" s="1">
         <v>46237.838541666664</v>
       </c>
       <c r="J161" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>11</v>
@@ -4888,13 +4888,13 @@
         <v>12</v>
       </c>
       <c r="H162" s="2">
-        <v>1.3888888888888889E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I162" s="1">
         <v>46237.839236111111</v>
       </c>
       <c r="J162" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>11</v>
@@ -4922,16 +4922,16 @@
         <v>20</v>
       </c>
       <c r="G164" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H164" s="2">
-        <v>1.25E-3</v>
+        <v>7.7546296296296295E-3</v>
       </c>
       <c r="I164" s="1">
         <v>46237.839930555558</v>
       </c>
       <c r="J164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>11</v>
@@ -4941,9 +4941,7 @@
       <c r="H165" s="2"/>
       <c r="I165" s="1"/>
       <c r="J165" s="2"/>
-      <c r="K165" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="K165" s="1"/>
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H166" s="2"/>
@@ -4993,7 +4991,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -5023,7 +5021,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5083,7 +5081,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5191,7 +5189,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5383,7 +5381,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -5899,7 +5897,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -5965,7 +5963,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -5977,7 +5975,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6073,7 +6071,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6085,7 +6083,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6181,7 +6179,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6241,7 +6239,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -15655,6 +15653,7 @@
       <c r="K1957" s="1"/>
     </row>
     <row r="1958" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
       <c r="K1958" s="1"/>
     </row>
@@ -15692,6 +15691,7 @@
       <c r="K1964" s="1"/>
     </row>
     <row r="1965" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
       <c r="K1965" s="1"/>
     </row>
@@ -15756,6 +15756,7 @@
       <c r="K1976" s="1"/>
     </row>
     <row r="1977" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:11" x14ac:dyDescent="0.25">
@@ -15787,11 +15788,11 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
     <row r="1984" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
       <c r="K1984" s="1"/>
     </row>
@@ -15802,6 +15803,7 @@
       <c r="K1985" s="1"/>
     </row>
     <row r="1986" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
       <c r="K1986" s="1"/>
     </row>
@@ -15877,6 +15879,7 @@
       <c r="K1999" s="1"/>
     </row>
     <row r="2000" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
       <c r="K2000" s="1"/>
     </row>
@@ -15887,6 +15890,7 @@
       <c r="K2001" s="1"/>
     </row>
     <row r="2002" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:11" x14ac:dyDescent="0.25">
@@ -15918,7 +15922,6 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -45211,6 +45214,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45503,6 +45507,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -45813,6 +45819,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -45937,6 +45944,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -45948,6 +45956,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46096,6 +46105,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -46106,10 +46116,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -46143,15 +46155,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -46192,18 +46207,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46219,6 +46238,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -46228,10 +46248,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -46267,10 +46289,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -46296,6 +46320,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -46310,6 +46335,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46344,6 +46370,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -46353,6 +46380,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -46362,6 +46390,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -46376,15 +46405,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -46414,6 +46444,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46434,11 +46465,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -46447,6 +46480,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -46476,6 +46510,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -46485,10 +46520,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -46503,14 +46540,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -46530,10 +46570,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -46553,9 +46595,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -46590,18 +46635,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46616,12 +46665,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -46636,10 +46685,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -46659,6 +46710,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -46678,6 +46730,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -46687,6 +46740,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -46732,6 +46786,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -46741,6 +46796,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -46755,6 +46811,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -46764,10 +46821,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -46782,6 +46841,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -46791,6 +46851,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -46810,6 +46871,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -46829,10 +46891,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -46842,6 +46906,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -46852,10 +46917,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -46870,18 +46937,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -46901,10 +46972,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -46924,6 +46997,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -46954,7 +47028,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -46969,10 +47042,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -46987,6 +47062,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -47001,11 +47077,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47015,6 +47091,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -47030,6 +47107,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -47044,6 +47122,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47064,6 +47143,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -47089,11 +47169,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -47112,15 +47194,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -47130,6 +47213,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -47149,6 +47233,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -47163,6 +47248,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -47182,10 +47268,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47195,6 +47283,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -47205,6 +47294,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -47241,7 +47331,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -47250,6 +47339,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -47263,10 +47353,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Reed-Beverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63E93BFE-4D33-4751-B334-5E1C156FFD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96B6F5E5-0009-45AF-A6BF-EB8AC05337E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="64">
   <si>
     <t>Company Name</t>
   </si>
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -812,7 +812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>22</v>
       </c>
@@ -907,7 +907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1374,7 +1374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>22</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>22</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>22</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>22</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>22</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>22</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>22</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -3940,7 +3940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>22</v>
       </c>
@@ -4769,10 +4769,10 @@
         <v>20</v>
       </c>
       <c r="G158" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H158" s="2">
-        <v>0</v>
+        <v>9.2592592592592588E-5</v>
       </c>
       <c r="I158" s="1">
         <v>46237.837152777778</v>
@@ -4785,32 +4785,11 @@
       </c>
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B159" t="s">
-        <v>22</v>
-      </c>
-      <c r="C159">
-        <v>5582</v>
-      </c>
-      <c r="D159" t="s">
-        <v>56</v>
-      </c>
-      <c r="F159" t="s">
-        <v>20</v>
-      </c>
-      <c r="G159" t="s">
-        <v>13</v>
-      </c>
-      <c r="H159" s="2">
-        <v>0</v>
-      </c>
-      <c r="I159" s="1">
-        <v>46237.837847222225</v>
-      </c>
-      <c r="J159" s="2">
-        <v>3</v>
-      </c>
+      <c r="H159" s="2"/>
+      <c r="I159" s="1"/>
+      <c r="J159" s="2"/>
       <c r="K159" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
@@ -4818,10 +4797,10 @@
         <v>22</v>
       </c>
       <c r="C160">
-        <v>5328</v>
+        <v>5582</v>
       </c>
       <c r="D160" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F160" t="s">
         <v>20</v>
@@ -4833,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="I160" s="1">
-        <v>46237.838541666664</v>
+        <v>46237.837847222225</v>
       </c>
       <c r="J160" s="2">
         <v>3</v>
@@ -4847,25 +4826,25 @@
         <v>22</v>
       </c>
       <c r="C161">
-        <v>5326</v>
+        <v>5328</v>
       </c>
       <c r="D161" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F161" t="s">
         <v>20</v>
       </c>
       <c r="G161" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H161" s="2">
-        <v>5.9490740740740745E-3</v>
+        <v>0</v>
       </c>
       <c r="I161" s="1">
         <v>46237.838541666664</v>
       </c>
       <c r="J161" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>11</v>
@@ -4876,72 +4855,95 @@
         <v>22</v>
       </c>
       <c r="C162">
-        <v>5319</v>
+        <v>5326</v>
       </c>
       <c r="D162" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F162" t="s">
         <v>20</v>
       </c>
       <c r="G162" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H162" s="2">
-        <v>2.199074074074074E-4</v>
+        <v>5.9490740740740745E-3</v>
       </c>
       <c r="I162" s="1">
-        <v>46237.839236111111</v>
+        <v>46237.838541666664</v>
       </c>
       <c r="J162" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H163" s="2"/>
-      <c r="I163" s="1"/>
-      <c r="J163" s="2"/>
+      <c r="B163" t="s">
+        <v>22</v>
+      </c>
+      <c r="C163">
+        <v>5319</v>
+      </c>
+      <c r="D163" t="s">
+        <v>24</v>
+      </c>
+      <c r="F163" t="s">
+        <v>20</v>
+      </c>
+      <c r="G163" t="s">
+        <v>12</v>
+      </c>
+      <c r="H163" s="2">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I163" s="1">
+        <v>46237.839236111111</v>
+      </c>
+      <c r="J163" s="2">
+        <v>3</v>
+      </c>
       <c r="K163" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H164" s="2"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="2"/>
+      <c r="K164" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B164" t="s">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
         <v>22</v>
       </c>
-      <c r="C164">
+      <c r="C165">
         <v>5347</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D165" t="s">
         <v>27</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F165" t="s">
         <v>20</v>
       </c>
-      <c r="G164" t="s">
+      <c r="G165" t="s">
         <v>10</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H165" s="2">
         <v>7.7546296296296295E-3</v>
       </c>
-      <c r="I164" s="1">
+      <c r="I165" s="1">
         <v>46237.839930555558</v>
       </c>
-      <c r="J164" s="2">
+      <c r="J165" s="2">
         <v>1</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K165" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H165" s="2"/>
-      <c r="I165" s="1"/>
-      <c r="J165" s="2"/>
-      <c r="K165" s="1"/>
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H166" s="2"/>
@@ -4991,7 +4993,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -5021,7 +5023,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5081,7 +5083,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5189,7 +5191,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5381,7 +5383,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -5897,7 +5899,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -5963,7 +5965,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -5975,7 +5977,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6071,7 +6073,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6083,7 +6085,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6179,7 +6181,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6239,7 +6241,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -15640,6 +15642,7 @@
       <c r="K1954" s="1"/>
     </row>
     <row r="1955" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
       <c r="K1955" s="1"/>
     </row>
@@ -15649,6 +15652,7 @@
       <c r="K1956" s="1"/>
     </row>
     <row r="1957" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
       <c r="K1957" s="1"/>
     </row>
@@ -15788,6 +15792,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -15841,7 +15846,6 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -45214,7 +45218,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45507,8 +45510,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -45819,7 +45820,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -45944,7 +45944,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -45956,7 +45955,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46105,35 +46103,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46144,44 +46136,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46192,37 +46175,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46233,52 +46209,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46289,17 +46255,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46310,32 +46273,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46345,106 +46302,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46454,7 +46391,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46465,127 +46401,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46595,62 +46505,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46670,67 +46567,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -46740,38 +46624,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -46786,117 +46663,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -46905,99 +46759,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47007,23 +46842,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -47032,52 +46863,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -47091,38 +46912,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47132,7 +46946,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -47143,23 +46956,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47169,37 +46978,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -47208,72 +47010,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47283,76 +47071,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Reed-Beverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96B6F5E5-0009-45AF-A6BF-EB8AC05337E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1BF95EE-B8F8-4595-876A-CA15050FEAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -45218,6 +45218,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45510,6 +45511,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -45820,6 +45823,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -45944,6 +45948,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -45955,6 +45960,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46103,29 +46109,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46136,35 +46148,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46175,30 +46196,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46209,42 +46237,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46255,14 +46293,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46273,26 +46314,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46302,86 +46349,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46391,6 +46459,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46401,101 +46470,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46505,49 +46600,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46562,59 +46670,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -46624,31 +46746,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -46658,99 +46787,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -46759,80 +46912,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -46842,67 +47014,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -46912,31 +47100,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -46946,6 +47141,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -46956,19 +47152,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -46978,90 +47178,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47071,51 +47293,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
